--- a/src/test/resources/testdata/demoqa-login-data-simple.xlsx
+++ b/src/test/resources/testdata/demoqa-login-data-simple.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Capgemini Training\MCP\src\test\resources\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CC9984-E49C-4900-89C0-F3C6A3201CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="21792" windowHeight="11628"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>username</t>
   </si>
@@ -86,9 +80,6 @@
   </si>
   <si>
     <t>wrongpass9</t>
-  </si>
-  <si>
-    <t>success</t>
   </si>
   <si>
     <t>wronguser10</t>
@@ -100,7 +91,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -189,7 +180,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -241,7 +232,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -435,19 +426,19 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.796875" customWidth="1"/>
-    <col min="2" max="2" width="17.265625" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -557,18 +548,18 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
